--- a/test-cases/Demoblaze_TestCases_Login_Cart.xlsx
+++ b/test-cases/Demoblaze_TestCases_Login_Cart.xlsx
@@ -1,36 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Tools\project\demoblaze-qa-automation\test-cases\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0902C050-3877-492A-B740-F758B47DC4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Login" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cart" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Order" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Login" sheetId="2" r:id="rId2"/>
+    <sheet name="Cart" sheetId="3" r:id="rId3"/>
+    <sheet name="Order" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Cart!$A$1:$O$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Login!$A$1:$O$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Cart!$A$1:$O$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Order!$A$1:$O$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Login!$A$1:$O$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Cart!$A$1:$O$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Order!$A$1:$O$15</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="364">
-  <si>
-    <t xml:space="preserve">Demoblaze – Test Case Suite (Login, Cart &amp; Order)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="366">
+  <si>
+    <t>Demoblaze – Test Case Suite (Login, Cart &amp; Order)</t>
   </si>
   <si>
     <t>Application</t>
@@ -42,13 +56,13 @@
     <t>Scope</t>
   </si>
   <si>
-    <t xml:space="preserve">Login, Cart, Order (Place Order from cart)</t>
+    <t>Login, Cart, Order (Place Order from cart)</t>
   </si>
   <si>
     <t>Author</t>
   </si>
   <si>
-    <t xml:space="preserve">Nolan Tran</t>
+    <t>Nolan Tran</t>
   </si>
   <si>
     <t>Version</t>
@@ -90,7 +104,7 @@
     <t>Order</t>
   </si>
   <si>
-    <t xml:space="preserve">Execution status</t>
+    <t>Execution status</t>
   </si>
   <si>
     <t>Pass</t>
@@ -102,16 +116,16 @@
     <t>Blocked</t>
   </si>
   <si>
-    <t xml:space="preserve">Not Run</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pass rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Execution rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC ID</t>
+    <t>Not Run</t>
+  </si>
+  <si>
+    <t>Pass rate</t>
+  </si>
+  <si>
+    <t>Execution rate</t>
+  </si>
+  <si>
+    <t>TC ID</t>
   </si>
   <si>
     <t>Sub-feature</t>
@@ -129,25 +143,25 @@
     <t>Preconditions</t>
   </si>
   <si>
-    <t xml:space="preserve">Test Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Steps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected Result</t>
+    <t>Test Data</t>
+  </si>
+  <si>
+    <t>Test Steps</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
   </si>
   <si>
     <t>Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Planned Spec</t>
+    <t>Planned Spec</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t xml:space="preserve">Actual Result</t>
+    <t>Actual Result</t>
   </si>
   <si>
     <t>Notes</t>
@@ -156,26 +170,26 @@
     <t>LG-001</t>
   </si>
   <si>
-    <t xml:space="preserve">Login modal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login modal opens from navbar</t>
+    <t>Login modal</t>
+  </si>
+  <si>
+    <t>Login modal opens from navbar</t>
   </si>
   <si>
     <t>High</t>
   </si>
   <si>
-    <t xml:space="preserve">Browser open at https://www.demoblaze.com/
+    <t>Browser open at https://www.demoblaze.com/
 User is NOT logged in</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click 'Log in' in the navbar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login modal is displayed with title 'Log in', Username field, Password field, 'Close' and 'Log in' buttons</t>
+    <t>1. Click 'Log in' in the navbar</t>
+  </si>
+  <si>
+    <t>Login modal is displayed with title 'Log in', Username field, Password field, 'Close' and 'Log in' buttons</t>
   </si>
   <si>
     <t>UI</t>
@@ -190,27 +204,27 @@
     <t>Authentication</t>
   </si>
   <si>
-    <t xml:space="preserve">Login with valid credentials</t>
+    <t>Login with valid credentials</t>
   </si>
   <si>
     <t>Critical</t>
   </si>
   <si>
-    <t xml:space="preserve">A registered account exists (TEST_USERNAME / TEST_PASSWORD)
+    <t>A registered account exists (TEST_USERNAME / TEST_PASSWORD)
 User is NOT logged in</t>
   </si>
   <si>
-    <t xml:space="preserve">Username: &lt;TEST_USERNAME&gt;
+    <t>Username: &lt;TEST_USERNAME&gt;
 Password: &lt;TEST_PASSWORD&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click 'Log in'
+    <t>1. Click 'Log in'
 2. Enter valid username
 3. Enter valid password
 4. Click 'Log in' button</t>
   </si>
   <si>
-    <t xml:space="preserve">No error alert
+    <t>No error alert
 Modal closes
 Navbar shows 'Welcome &lt;username&gt;'
 'Log out' is visible; 'Log in' and 'Sign up' are hidden</t>
@@ -225,17 +239,17 @@
     <t>Session</t>
   </si>
   <si>
-    <t xml:space="preserve">Session persists after page reload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LG-002 completed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Log in successfully
+    <t>Session persists after page reload</t>
+  </si>
+  <si>
+    <t>LG-002 completed</t>
+  </si>
+  <si>
+    <t>1. Log in successfully
 2. Reload the page (F5)</t>
   </si>
   <si>
-    <t xml:space="preserve">User remains logged in; 'Welcome &lt;username&gt;' still displayed</t>
+    <t>User remains logged in; 'Welcome &lt;username&gt;' still displayed</t>
   </si>
   <si>
     <t>tests/e2e/login/session.spec.ts</t>
@@ -244,19 +258,19 @@
     <t>LG-004</t>
   </si>
   <si>
-    <t xml:space="preserve">Session persists across pages</t>
+    <t>Session persists across pages</t>
   </si>
   <si>
     <t>Medium</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Log in successfully
+    <t>1. Log in successfully
 2. Open a product page
 3. Open Cart page
 4. Return to Home</t>
   </si>
   <si>
-    <t xml:space="preserve">'Welcome &lt;username&gt;' displayed on every page</t>
+    <t>'Welcome &lt;username&gt;' displayed on every page</t>
   </si>
   <si>
     <t>LG-005</t>
@@ -265,17 +279,17 @@
     <t>Logout</t>
   </si>
   <si>
-    <t xml:space="preserve">Logout ends the session</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is logged in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Log out'
+    <t>Logout ends the session</t>
+  </si>
+  <si>
+    <t>User is logged in</t>
+  </si>
+  <si>
+    <t>1. Click 'Log out'
 2. Reload the page</t>
   </si>
   <si>
-    <t xml:space="preserve">'Welcome &lt;username&gt;' and 'Log out' are hidden
+    <t>'Welcome &lt;username&gt;' and 'Log out' are hidden
 'Log in' and 'Sign up' are visible
 User stays logged out after reload</t>
   </si>
@@ -283,81 +297,81 @@
     <t>LG-006</t>
   </si>
   <si>
-    <t xml:space="preserve">Close modal without logging in</t>
+    <t>Close modal without logging in</t>
   </si>
   <si>
     <t>Low</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click 'Log in'
+    <t>1. Click 'Log in'
 2. Enter credentials
 3. Click 'Close' (or X)</t>
   </si>
   <si>
-    <t xml:space="preserve">Modal closes; no login request is sent; user remains logged out</t>
+    <t>Modal closes; no login request is sent; user remains logged out</t>
   </si>
   <si>
     <t>LG-007</t>
   </si>
   <si>
-    <t xml:space="preserve">Password input is masked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Password: Secret123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Log in'
+    <t>Password input is masked</t>
+  </si>
+  <si>
+    <t>Password: Secret123</t>
+  </si>
+  <si>
+    <t>1. Click 'Log in'
 2. Type a password</t>
   </si>
   <si>
-    <t xml:space="preserve">Password field has type='password'; characters are masked</t>
+    <t>Password field has type='password'; characters are masked</t>
   </si>
   <si>
     <t>LG-008</t>
   </si>
   <si>
-    <t xml:space="preserve">Login with Unicode / special-character username</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An account exists whose username contains Unicode and special characters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username: qa_ñgườidùng_#1
+    <t>Login with Unicode / special-character username</t>
+  </si>
+  <si>
+    <t>An account exists whose username contains Unicode and special characters</t>
+  </si>
+  <si>
+    <t>Username: qa_ñgườidùng_#1
 Password: &lt;valid&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Login modal
+    <t>1. Open Login modal
 2. Enter the Unicode username and valid password
 3. Click 'Log in'</t>
   </si>
   <si>
-    <t xml:space="preserve">Login succeeds; 'Welcome &lt;username&gt;' renders the characters correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account is created via API in test setup</t>
+    <t>Login succeeds; 'Welcome &lt;username&gt;' renders the characters correctly</t>
+  </si>
+  <si>
+    <t>Account is created via API in test setup</t>
   </si>
   <si>
     <t>LG-009</t>
   </si>
   <si>
-    <t xml:space="preserve">Login request does not send plain-text password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid credentials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open DevTools Network (or intercept request)
+    <t>Login request does not send plain-text password</t>
+  </si>
+  <si>
+    <t>Valid credentials</t>
+  </si>
+  <si>
+    <t>1. Open DevTools Network (or intercept request)
 2. Log in
 3. Inspect POST /login payload</t>
   </si>
   <si>
-    <t xml:space="preserve">Payload 'password' field is not the plain-text password (it is encoded)</t>
+    <t>Payload 'password' field is not the plain-text password (it is encoded)</t>
   </si>
   <si>
     <t>tests/e2e/login/security.spec.ts</t>
   </si>
   <si>
-    <t xml:space="preserve">Encoding is Base64, which is not encryption; transport security relies on HTTPS</t>
+    <t>Encoding is Base64, which is not encryption; transport security relies on HTTPS</t>
   </si>
   <si>
     <t>LG-010</t>
@@ -366,19 +380,19 @@
     <t>Validation</t>
   </si>
   <si>
-    <t xml:space="preserve">Login with empty username and password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username: (empty)
+    <t>Login with empty username and password</t>
+  </si>
+  <si>
+    <t>Username: (empty)
 Password: (empty)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Login modal
+    <t>1. Open Login modal
 2. Leave both fields empty
 3. Click 'Log in'</t>
   </si>
   <si>
-    <t xml:space="preserve">Alert 'Please fill out Username and Password.' is shown; user not logged in</t>
+    <t>Alert 'Please fill out Username and Password.' is shown; user not logged in</t>
   </si>
   <si>
     <t>tests/e2e/login/validation.spec.ts</t>
@@ -387,14 +401,14 @@
     <t>LG-011</t>
   </si>
   <si>
-    <t xml:space="preserve">Login with empty username</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username: (empty)
+    <t>Login with empty username</t>
+  </si>
+  <si>
+    <t>Username: (empty)
 Password: &lt;TEST_PASSWORD&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Login modal
+    <t>1. Open Login modal
 2. Enter only password
 3. Click 'Log in'</t>
   </si>
@@ -402,14 +416,14 @@
     <t>LG-012</t>
   </si>
   <si>
-    <t xml:space="preserve">Login with empty password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username: &lt;TEST_USERNAME&gt;
+    <t>Login with empty password</t>
+  </si>
+  <si>
+    <t>Username: &lt;TEST_USERNAME&gt;
 Password: (empty)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Login modal
+    <t>1. Open Login modal
 2. Enter only username
 3. Click 'Log in'</t>
   </si>
@@ -417,57 +431,57 @@
     <t>LG-013</t>
   </si>
   <si>
-    <t xml:space="preserve">Login with wrong password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username: &lt;TEST_USERNAME&gt;
+    <t>Login with wrong password</t>
+  </si>
+  <si>
+    <t>Username: &lt;TEST_USERNAME&gt;
 Password: WrongPass!123</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Login modal
+    <t>1. Open Login modal
 2. Enter valid username, wrong password
 3. Click 'Log in'</t>
   </si>
   <si>
-    <t xml:space="preserve">Alert 'Wrong password.' is shown; user not logged in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI + API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests/e2e/login/authentication.spec.ts
+    <t>Alert 'Wrong password.' is shown; user not logged in</t>
+  </si>
+  <si>
+    <t>UI + API</t>
+  </si>
+  <si>
+    <t>tests/e2e/login/authentication.spec.ts
 tests/integration/auth.api.spec.ts</t>
   </si>
   <si>
     <t>LG-014</t>
   </si>
   <si>
-    <t xml:space="preserve">Login with non-existent username</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username: nouser_&lt;timestamp&gt;
+    <t>Login with non-existent username</t>
+  </si>
+  <si>
+    <t>Username: nouser_&lt;timestamp&gt;
 Password: any</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Login modal
+    <t>1. Open Login modal
 2. Enter an unregistered username
 3. Click 'Log in'</t>
   </si>
   <si>
-    <t xml:space="preserve">Alert 'User does not exist.' is shown; user not logged in</t>
+    <t>Alert 'User does not exist.' is shown; user not logged in</t>
   </si>
   <si>
     <t>LG-015</t>
   </si>
   <si>
-    <t xml:space="preserve">Password is case-sensitive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username: &lt;TEST_USERNAME&gt;
+    <t>Password is case-sensitive</t>
+  </si>
+  <si>
+    <t>Username: &lt;TEST_USERNAME&gt;
 Password: &lt;TEST_PASSWORD&gt; with inverted letter case</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Login modal
+    <t>1. Open Login modal
 2. Enter valid username and password with changed case
 3. Click 'Log in'</t>
   </si>
@@ -475,22 +489,22 @@
     <t>LG-016</t>
   </si>
   <si>
-    <t xml:space="preserve">Whitespace-only username and password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username: '   '
+    <t>Whitespace-only username and password</t>
+  </si>
+  <si>
+    <t>Username: '   '
 Password: '   '</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Login modal
+    <t>1. Open Login modal
 2. Enter only spaces in both fields
 3. Click 'Log in'</t>
   </si>
   <si>
-    <t xml:space="preserve">Input treated as empty: validation alert shown, no login request is accepted; user not logged in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alert 'Wrong password.' shown; whitespace input is sent to the API and an account with a whitespace-only username exists</t>
+    <t>Input treated as empty: validation alert shown, no login request is accepted; user not logged in</t>
+  </si>
+  <si>
+    <t>Alert 'Wrong password.' shown; whitespace input is sent to the API and an account with a whitespace-only username exists</t>
   </si>
   <si>
     <t>LG-017</t>
@@ -499,145 +513,145 @@
     <t>Security</t>
   </si>
   <si>
-    <t xml:space="preserve">SQL injection string in username</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username: ' OR '1'='1
+    <t>SQL injection string in username</t>
+  </si>
+  <si>
+    <t>Username: ' OR '1'='1
 Password: ' OR '1'='1</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Login modal
+    <t>1. Open Login modal
 2. Enter the injection strings
 3. Click 'Log in'</t>
   </si>
   <si>
-    <t xml:space="preserve">Login fails with an error alert; no server error, no session created</t>
+    <t>Login fails with an error alert; no server error, no session created</t>
   </si>
   <si>
     <t>LG-018</t>
   </si>
   <si>
-    <t xml:space="preserve">XSS payload in username</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username: &lt;img src=x onerror=alert('xss')&gt;
+    <t>XSS payload in username</t>
+  </si>
+  <si>
+    <t>Username: &lt;img src=x onerror=alert('xss')&gt;
 Password: any</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Login modal
+    <t>1. Open Login modal
 2. Enter the payload
 3. Click 'Log in'</t>
   </si>
   <si>
-    <t xml:space="preserve">Payload is not executed (no 'xss' dialog, no injected element); login fails with an error alert</t>
+    <t>Payload is not executed (no 'xss' dialog, no injected element); login fails with an error alert</t>
   </si>
   <si>
     <t>LG-019</t>
   </si>
   <si>
-    <t xml:space="preserve">Username with leading/trailing spaces</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username: '  &lt;TEST_USERNAME&gt;  '
+    <t>Username with leading/trailing spaces</t>
+  </si>
+  <si>
+    <t>Username: '  &lt;TEST_USERNAME&gt;  '
 Password: &lt;TEST_PASSWORD&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Login modal
+    <t>1. Open Login modal
 2. Enter username surrounded by spaces, valid password
 3. Click 'Log in'</t>
   </si>
   <si>
-    <t xml:space="preserve">System applies one consistent rule: either input is trimmed and login succeeds, or login fails with an error alert. No partial/broken session</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm trimming rule with BA</t>
+    <t>System applies one consistent rule: either input is trimmed and login succeeds, or login fails with an error alert. No partial/broken session</t>
+  </si>
+  <si>
+    <t>Confirm trimming rule with BA</t>
   </si>
   <si>
     <t>LG-020</t>
   </si>
   <si>
-    <t xml:space="preserve">Username in different letter case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username: &lt;TEST_USERNAME&gt; in UPPER CASE
+    <t>Username in different letter case</t>
+  </si>
+  <si>
+    <t>Username: &lt;TEST_USERNAME&gt; in UPPER CASE
 Password: &lt;TEST_PASSWORD&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Login modal
+    <t>1. Open Login modal
 2. Enter upper-cased username, valid password
 3. Click 'Log in'</t>
   </si>
   <si>
-    <t xml:space="preserve">Login fails with an error alert (usernames are case-sensitive); user not logged in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm case-sensitivity rule with BA</t>
+    <t>Login fails with an error alert (usernames are case-sensitive); user not logged in</t>
+  </si>
+  <si>
+    <t>Confirm case-sensitivity rule with BA</t>
   </si>
   <si>
     <t>LG-021</t>
   </si>
   <si>
-    <t xml:space="preserve">Very long username (2000 characters)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username: 'a' x 300
+    <t>Very long username (2000 characters)</t>
+  </si>
+  <si>
+    <t>Username: 'a' x 300
 Password: any</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open Login modal
+    <t>1. Open Login modal
 2. Enter the long username
 3. Click 'Log in'</t>
   </si>
   <si>
-    <t xml:space="preserve">Error alert shown; page remains responsive; no server error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No alert is shown, the Log in modal stays open and the user gets no feedback.</t>
+    <t>Error alert shown; page remains responsive; no server error</t>
+  </si>
+  <si>
+    <t>No alert is shown, the Log in modal stays open and the user gets no feedback.</t>
   </si>
   <si>
     <t>LG-022</t>
   </si>
   <si>
-    <t xml:space="preserve">Double-click 'Log in' button</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open Login modal
+    <t>Double-click 'Log in' button</t>
+  </si>
+  <si>
+    <t>1. Open Login modal
 2. Enter valid credentials
 3. Double-click 'Log in' quickly</t>
   </si>
   <si>
-    <t xml:space="preserve">User logged in once; 'Welcome &lt;username&gt;' shown; no error alert</t>
+    <t>User logged in once; 'Welcome &lt;username&gt;' shown; no error alert</t>
   </si>
   <si>
     <t>LG-023</t>
   </si>
   <si>
-    <t xml:space="preserve">Logout in one tab invalidates other tab after reload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User logged in in two tabs of the same browser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. In tab A click 'Log out'
+    <t>Logout in one tab invalidates other tab after reload</t>
+  </si>
+  <si>
+    <t>User logged in in two tabs of the same browser</t>
+  </si>
+  <si>
+    <t>1. In tab A click 'Log out'
 2. In tab B reload the page</t>
   </si>
   <si>
-    <t xml:space="preserve">Tab B shows logged-out state ('Log in' visible)</t>
+    <t>Tab B shows logged-out state ('Log in' visible)</t>
   </si>
   <si>
     <t>LG-024</t>
   </si>
   <si>
-    <t xml:space="preserve">Auth token cookie lifecycle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Log in
+    <t>Auth token cookie lifecycle</t>
+  </si>
+  <si>
+    <t>1. Log in
 2. Inspect cookies
 3. Log out
 4. Inspect cookies</t>
   </si>
   <si>
-    <t xml:space="preserve">After login an auth token cookie (tokenp_) exists; after logout it is removed</t>
+    <t>After login an auth token cookie (tokenp_) exists; after logout it is removed</t>
   </si>
   <si>
     <t>LG-025</t>
@@ -646,19 +660,19 @@
     <t>API</t>
   </si>
   <si>
-    <t xml:space="preserve">POST /login with valid credentials returns token</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A registered account exists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{ username, password: base64(password) }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Send POST https://api.demoblaze.com/login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP 200; body contains 'Auth_token: &lt;token&gt;'; token validates via POST /check</t>
+    <t>POST /login with valid credentials returns token</t>
+  </si>
+  <si>
+    <t>A registered account exists</t>
+  </si>
+  <si>
+    <t>{ username, password: base64(password) }</t>
+  </si>
+  <si>
+    <t>1. Send POST https://api.demoblaze.com/login</t>
+  </si>
+  <si>
+    <t>HTTP 200; body contains 'Auth_token: &lt;token&gt;'; token validates via POST /check</t>
   </si>
   <si>
     <t>tests/integration/auth.api.spec.ts</t>
@@ -667,22 +681,22 @@
     <t>CT-001</t>
   </si>
   <si>
-    <t xml:space="preserve">Add to cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guest adds a product to cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product: Samsung galaxy s6 ($360)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click product 'Samsung galaxy s6'
+    <t>Add to cart</t>
+  </si>
+  <si>
+    <t>Guest adds a product to cart</t>
+  </si>
+  <si>
+    <t>Product: Samsung galaxy s6 ($360)</t>
+  </si>
+  <si>
+    <t>1. Click product 'Samsung galaxy s6'
 2. Click 'Add to cart'
 3. Accept the alert
 4. Open 'Cart'</t>
   </si>
   <si>
-    <t xml:space="preserve">Alert 'Product added' shown
+    <t>Alert 'Product added' shown
 Cart shows 1 row: title 'Samsung galaxy s6', price 360
 Total = 360</t>
   </si>
@@ -693,80 +707,80 @@
     <t>CT-002</t>
   </si>
   <si>
-    <t xml:space="preserve">Logged-in user adds a product to cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is logged in with a registered account
+    <t>Logged-in user adds a product to cart</t>
+  </si>
+  <si>
+    <t>User is logged in with a registered account
 Cart of that account is empty</t>
   </si>
   <si>
-    <t xml:space="preserve">Product: Nokia lumia 1520 ($820)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open product 'Nokia lumia 1520'
+    <t>Product: Nokia lumia 1520 ($820)</t>
+  </si>
+  <si>
+    <t>1. Open product 'Nokia lumia 1520'
 2. Click 'Add to cart'
 3. Accept alert
 4. Open 'Cart'</t>
   </si>
   <si>
-    <t xml:space="preserve">Cart shows 1 row: 'Nokia lumia 1520', price 820
+    <t>Cart shows 1 row: 'Nokia lumia 1520', price 820
 Total = 820</t>
   </si>
   <si>
     <t>CT-003</t>
   </si>
   <si>
-    <t xml:space="preserve">Add multiple different products</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung galaxy s6 ($360), Nokia lumia 1520 ($820), Sony vaio i5 ($790)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add each product to cart
+    <t>Add multiple different products</t>
+  </si>
+  <si>
+    <t>Samsung galaxy s6 ($360), Nokia lumia 1520 ($820), Sony vaio i5 ($790)</t>
+  </si>
+  <si>
+    <t>1. Add each product to cart
 2. Open 'Cart'</t>
   </si>
   <si>
-    <t xml:space="preserve">3 rows listed with correct titles and prices
+    <t>3 rows listed with correct titles and prices
 Total = 1970 (sum of prices)</t>
   </si>
   <si>
     <t>CT-004</t>
   </si>
   <si>
-    <t xml:space="preserve">Add the same product twice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung galaxy s6 ($360) x2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add 'Samsung galaxy s6' to cart twice
+    <t>Add the same product twice</t>
+  </si>
+  <si>
+    <t>Samsung galaxy s6 ($360) x2</t>
+  </si>
+  <si>
+    <t>1. Add 'Samsung galaxy s6' to cart twice
 2. Open 'Cart'</t>
   </si>
   <si>
-    <t xml:space="preserve">2 rows of 'Samsung galaxy s6'
+    <t>2 rows of 'Samsung galaxy s6'
 Total = 720</t>
   </si>
   <si>
-    <t xml:space="preserve">Cart has no quantity field; each add creates a row</t>
+    <t>Cart has no quantity field; each add creates a row</t>
   </si>
   <si>
     <t>CT-005</t>
   </si>
   <si>
-    <t xml:space="preserve">Remove item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delete one item from cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cart contains: Samsung galaxy s6 ($360), Nokia lumia 1520 ($820)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open 'Cart'
+    <t>Remove item</t>
+  </si>
+  <si>
+    <t>Delete one item from cart</t>
+  </si>
+  <si>
+    <t>Cart contains: Samsung galaxy s6 ($360), Nokia lumia 1520 ($820)</t>
+  </si>
+  <si>
+    <t>1. Open 'Cart'
 2. Click 'Delete' on 'Samsung galaxy s6'</t>
   </si>
   <si>
-    <t xml:space="preserve">Row 'Samsung galaxy s6' removed; 'Nokia lumia 1520' remains
+    <t>Row 'Samsung galaxy s6' removed; 'Nokia lumia 1520' remains
 Total = 820</t>
   </si>
   <si>
@@ -776,14 +790,14 @@
     <t>CT-006</t>
   </si>
   <si>
-    <t xml:space="preserve">Delete all items from cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open 'Cart'
+    <t>Delete all items from cart</t>
+  </si>
+  <si>
+    <t>1. Open 'Cart'
 2. Delete every row</t>
   </si>
   <si>
-    <t xml:space="preserve">Cart table is empty; Total is empty / 0</t>
+    <t>Cart table is empty; Total is empty / 0</t>
   </si>
   <si>
     <t>CT-007</t>
@@ -792,17 +806,17 @@
     <t>Persistence</t>
   </si>
   <si>
-    <t xml:space="preserve">Guest cart persists after reload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cart contains 1 product: Samsung galaxy s6 ($360) (guest)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open 'Cart'
+    <t>Guest cart persists after reload</t>
+  </si>
+  <si>
+    <t>Cart contains 1 product: Samsung galaxy s6 ($360) (guest)</t>
+  </si>
+  <si>
+    <t>1. Open 'Cart'
 2. Reload page</t>
   </si>
   <si>
-    <t xml:space="preserve">Same item and total shown after reload</t>
+    <t>Same item and total shown after reload</t>
   </si>
   <si>
     <t>tests/e2e/cart/persistence.spec.ts</t>
@@ -811,38 +825,38 @@
     <t>CT-008</t>
   </si>
   <si>
-    <t xml:space="preserve">Logged-in cart persists across sessions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung galaxy s6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add 'Samsung galaxy s6'
+    <t>Logged-in cart persists across sessions</t>
+  </si>
+  <si>
+    <t>Samsung galaxy s6</t>
+  </si>
+  <si>
+    <t>1. Add 'Samsung galaxy s6'
 2. Log out
 3. Close browser / open new browser context
 4. Log in again
 5. Open 'Cart'</t>
   </si>
   <si>
-    <t xml:space="preserve">Cart still contains 'Samsung galaxy s6'</t>
+    <t>Cart still contains 'Samsung galaxy s6'</t>
   </si>
   <si>
     <t>CT-009</t>
   </si>
   <si>
-    <t xml:space="preserve">Cart view</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cart table structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cart contains 1 product: Samsung galaxy s6 ($360)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open 'Cart'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table headers: Pic, Title, Price, x
+    <t>Cart view</t>
+  </si>
+  <si>
+    <t>Cart table structure</t>
+  </si>
+  <si>
+    <t>Cart contains 1 product: Samsung galaxy s6 ($360)</t>
+  </si>
+  <si>
+    <t>1. Open 'Cart'</t>
+  </si>
+  <si>
+    <t>Table headers: Pic, Title, Price, x
 Each row has image, title, price and 'Delete' link
 'Place Order' button visible</t>
   </si>
@@ -853,34 +867,34 @@
     <t>CT-010</t>
   </si>
   <si>
-    <t xml:space="preserve">Cart price matches product page price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product: MacBook air</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open product page, note price
+    <t>Cart price matches product page price</t>
+  </si>
+  <si>
+    <t>Product: MacBook air</t>
+  </si>
+  <si>
+    <t>1. Open product page, note price
 2. Add to cart
 3. Open 'Cart'</t>
   </si>
   <si>
-    <t xml:space="preserve">Price in cart equals price on product page (without '$' and '*includes tax')</t>
+    <t>Price in cart equals price on product page (without '$' and '*includes tax')</t>
   </si>
   <si>
     <t>CT-011</t>
   </si>
   <si>
-    <t xml:space="preserve">Products from different categories</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phone: Samsung galaxy s6; Laptop: Sony vaio i5; Monitor: Apple monitor 24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Filter by each category and add one product
+    <t>Products from different categories</t>
+  </si>
+  <si>
+    <t>Phone: Samsung galaxy s6; Laptop: Sony vaio i5; Monitor: Apple monitor 24</t>
+  </si>
+  <si>
+    <t>1. Filter by each category and add one product
 2. Open 'Cart'</t>
   </si>
   <si>
-    <t xml:space="preserve">3 rows, one per category; total = sum of the 3 prices</t>
+    <t>3 rows, one per category; total = sum of the 3 prices</t>
   </si>
   <si>
     <t>CT-012</t>
@@ -889,40 +903,40 @@
     <t>Isolation</t>
   </si>
   <si>
-    <t xml:space="preserve">Guest cart is not shared between sessions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two separate browser contexts (guest A, guest B)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Guest A adds 'Samsung galaxy s6'
+    <t>Guest cart is not shared between sessions</t>
+  </si>
+  <si>
+    <t>Two separate browser contexts (guest A, guest B)</t>
+  </si>
+  <si>
+    <t>1. Guest A adds 'Samsung galaxy s6'
 2. Guest B opens 'Cart'</t>
   </si>
   <si>
-    <t xml:space="preserve">Guest B's cart is empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests/e2e/cart/persistence.spec.ts
+    <t>Guest B's cart is empty</t>
+  </si>
+  <si>
+    <t>tests/e2e/cart/persistence.spec.ts
 tests/integration/cart.api.spec.ts</t>
   </si>
   <si>
     <t>CT-013</t>
   </si>
   <si>
-    <t xml:space="preserve">Users cannot see each other's carts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two registered accounts (user A, user B)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nokia lumia 1520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. User A adds 'Nokia lumia 1520'
+    <t>Users cannot see each other's carts</t>
+  </si>
+  <si>
+    <t>Two registered accounts (user A, user B)</t>
+  </si>
+  <si>
+    <t>Nokia lumia 1520</t>
+  </si>
+  <si>
+    <t>1. User A adds 'Nokia lumia 1520'
 2. User B views cart (UI or POST /viewcart)</t>
   </si>
   <si>
-    <t xml:space="preserve">User B's cart does not contain user A's item</t>
+    <t>User B's cart does not contain user A's item</t>
   </si>
   <si>
     <t>tests/integration/cart.api.spec.ts</t>
@@ -931,102 +945,99 @@
     <t>CT-014</t>
   </si>
   <si>
-    <t xml:space="preserve">Delete with invalid item id (API)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /deleteitem { id: 'non-existent-uuid' }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Send POST /deleteitem with an unknown id
+    <t>Delete with invalid item id (API)</t>
+  </si>
+  <si>
+    <t>POST /deleteitem { id: 'non-existent-uuid' }</t>
+  </si>
+  <si>
+    <t>1. Send POST /deleteitem with an unknown id
 2. POST /viewcart</t>
   </si>
   <si>
-    <t xml:space="preserve">No server error; existing cart item is not removed</t>
+    <t>No server error; existing cart item is not removed</t>
   </si>
   <si>
     <t>CT-015</t>
   </si>
   <si>
-    <t xml:space="preserve">Add many items (10) or max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 x add to cart via API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add 10 products
+    <t>Add many items (10) or max</t>
+  </si>
+  <si>
+    <t>10 x add to cart via API</t>
+  </si>
+  <si>
+    <t>1. Add 10 products
 2. Open 'Cart'</t>
   </si>
   <si>
-    <t xml:space="preserve">10 (max) rows listed; total equals sum of prices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Items seeded via API to speed up setup</t>
+    <t>10 (max) rows listed; total equals sum of prices</t>
+  </si>
+  <si>
+    <t>Items seeded via API to speed up setup</t>
   </si>
   <si>
     <t>CT-016</t>
   </si>
   <si>
-    <t xml:space="preserve">Delete one of two identical rows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cart contains 'Samsung galaxy s6' twice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open 'Cart'
+    <t>Delete one of two identical rows</t>
+  </si>
+  <si>
+    <t>Cart contains 'Samsung galaxy s6' twice</t>
+  </si>
+  <si>
+    <t>1. Open 'Cart'
 2. Delete one 'Samsung galaxy s6' row</t>
   </si>
   <si>
-    <t xml:space="preserve">Exactly 1 row remains; Total = 360</t>
+    <t>Exactly 1 row remains; Total = 360</t>
   </si>
   <si>
     <t>CT-017</t>
   </si>
   <si>
-    <t xml:space="preserve">Rapid double-click 'Add to cart'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. On product page double-click 'Add to cart' quickly
+    <t>Rapid double-click 'Add to cart'</t>
+  </si>
+  <si>
+    <t>1. On product page double-click 'Add to cart' quickly
 2. Open 'Cart'</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of rows equals number of successful 'Product added' alerts; cart total is consistent</t>
+    <t>Number of rows equals number of successful 'Product added' alerts; cart total is consistent</t>
   </si>
   <si>
     <t>CT-018</t>
   </si>
   <si>
-    <t xml:space="preserve">Add / view / delete cart item via API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guest cookie id generated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /addtocart, /viewcart, /deleteitem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. POST /addtocart {id, cookie, prod_id:1, flag:false}
+    <t>Add / view / delete cart item via API</t>
+  </si>
+  <si>
+    <t>Guest cookie id generated</t>
+  </si>
+  <si>
+    <t>POST /addtocart, /viewcart, /deleteitem</t>
+  </si>
+  <si>
+    <t>1. POST /addtocart {id, cookie, prod_id:1, flag:false}
 2. POST /viewcart
 3. POST /deleteitem {id}
 4. POST /viewcart</t>
   </si>
   <si>
-    <t xml:space="preserve">Step 2 returns the item with prod_id 1; after delete, step 4 returns no items</t>
+    <t>Step 2 returns the item with prod_id 1; after delete, step 4 returns no items</t>
   </si>
   <si>
     <t>OD-001</t>
   </si>
   <si>
-    <t xml:space="preserve">Place order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Place Order' opens order form with total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open 'Cart'
+    <t>Place order</t>
+  </si>
+  <si>
+    <t>1. Open 'Cart'
 2. Click 'Place Order'</t>
   </si>
   <si>
-    <t xml:space="preserve">Order modal shows 'Total: 360' and fields Name, Country, City, Credit card, Month, Year; buttons 'Close', 'Purchase'</t>
+    <t>Order modal shows 'Total: 360' and fields Name, Country, City, Credit card, Month, Year; buttons 'Close', 'Purchase'</t>
   </si>
   <si>
     <t>tests/e2e/order/purchase.spec.ts</t>
@@ -1035,10 +1046,10 @@
     <t>OD-002</t>
   </si>
   <si>
-    <t xml:space="preserve">Purchase with valid data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name: Nolan QA
+    <t>Purchase with valid data</t>
+  </si>
+  <si>
+    <t>Name: Nolan QA
 Country: Vietnam
 City: Hanoi
 Card: 4111111111111111
@@ -1046,28 +1057,28 @@
 Year: 2027</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open 'Cart' &gt; 'Place Order'
+    <t>1. Open 'Cart' &gt; 'Place Order'
 2. Fill all fields
 3. Click 'Purchase'</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirmation 'Thank you for your purchase!' shown with Id, Amount: 360 USD, Card Number, Name, Date</t>
+    <t>Confirmation 'Thank you for your purchase!' shown with Id, Amount: 360 USD, Card Number, Name, Date</t>
   </si>
   <si>
     <t>OD-003</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirmation details match the order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid order data as OD-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Place order with valid data
+    <t>Confirmation details match the order</t>
+  </si>
+  <si>
+    <t>Valid order data as OD-002</t>
+  </si>
+  <si>
+    <t>1. Place order with valid data
 2. Read the confirmation text</t>
   </si>
   <si>
-    <t xml:space="preserve">Amount = cart total (1180)
+    <t>Amount = cart total (1180)
 Card Number and Name equal the entered values
 Date = today's date</t>
   </si>
@@ -1075,34 +1086,34 @@
     <t>OD-004</t>
   </si>
   <si>
-    <t xml:space="preserve">Cart is emptied after purchase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid order data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete purchase
+    <t>Cart is emptied after purchase</t>
+  </si>
+  <si>
+    <t>Valid order data</t>
+  </si>
+  <si>
+    <t>1. Complete purchase
 2. Click 'OK'
 3. Open 'Cart'</t>
   </si>
   <si>
-    <t xml:space="preserve">Redirected to Home after 'OK'; Cart is empty</t>
+    <t>Redirected to Home after 'OK'; Cart is empty</t>
   </si>
   <si>
     <t>OD-005</t>
   </si>
   <si>
-    <t xml:space="preserve">Purchase with all fields empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All fields empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open 'Place Order'
+    <t>Purchase with all fields empty</t>
+  </si>
+  <si>
+    <t>All fields empty</t>
+  </si>
+  <si>
+    <t>1. Open 'Place Order'
 2. Click 'Purchase'</t>
   </si>
   <si>
-    <t xml:space="preserve">Alert 'Please fill out Name and Creditcard.'; no confirmation; cart unchanged</t>
+    <t>Alert 'Please fill out Name and Creditcard.'; no confirmation; cart unchanged</t>
   </si>
   <si>
     <t>tests/e2e/order/validation.spec.ts</t>
@@ -1111,30 +1122,30 @@
     <t>OD-006</t>
   </si>
   <si>
-    <t xml:space="preserve">Purchase without credit card</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name: Nolan QA, Card: (empty)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open 'Place Order'
+    <t>Purchase without credit card</t>
+  </si>
+  <si>
+    <t>Name: Nolan QA, Card: (empty)</t>
+  </si>
+  <si>
+    <t>1. Open 'Place Order'
 2. Fill Name only
 3. Click 'Purchase'</t>
   </si>
   <si>
-    <t xml:space="preserve">Alert 'Please fill out Name and Creditcard.'; no confirmation</t>
+    <t>Alert 'Please fill out Name and Creditcard.'; no confirmation</t>
   </si>
   <si>
     <t>OD-007</t>
   </si>
   <si>
-    <t xml:space="preserve">Purchase without name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name: (empty), Card: 4111111111111111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open 'Place Order'
+    <t>Purchase without name</t>
+  </si>
+  <si>
+    <t>Name: (empty), Card: 4111111111111111</t>
+  </si>
+  <si>
+    <t>1. Open 'Place Order'
 2. Fill Card only
 3. Click 'Purchase'</t>
   </si>
@@ -1142,160 +1153,171 @@
     <t>OD-008</t>
   </si>
   <si>
-    <t xml:space="preserve">Close order form without purchasing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open 'Place Order'
+    <t>Close order form without purchasing</t>
+  </si>
+  <si>
+    <t>1. Open 'Place Order'
 2. Fill fields
 3. Click 'Close'
 4. Reload Cart</t>
   </si>
   <si>
-    <t xml:space="preserve">Modal closes; no confirmation; cart still contains the item</t>
+    <t>Modal closes; no confirmation; cart still contains the item</t>
   </si>
   <si>
     <t>OD-009</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-numeric credit card number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card: abcd-efgh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open 'Place Order'
+    <t>Non-numeric credit card number</t>
+  </si>
+  <si>
+    <t>Card: abcd-efgh</t>
+  </si>
+  <si>
+    <t>1. Open 'Place Order'
 2. Enter Name and non-numeric card
 3. Click 'Purchase'</t>
   </si>
   <si>
-    <t xml:space="preserve">Purchase rejected with a card validation message; no confirmation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likely defect if purchase succeeds</t>
+    <t>Purchase rejected with a card validation message; no confirmation</t>
+  </si>
+  <si>
+    <t>Likely defect if purchase succeeds</t>
   </si>
   <si>
     <t>OD-010</t>
   </si>
   <si>
-    <t xml:space="preserve">Invalid month / past year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Month: 13; Year: 2000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open 'Place Order'
+    <t>Invalid month / past year</t>
+  </si>
+  <si>
+    <t>Month: 13; Year: 2000</t>
+  </si>
+  <si>
+    <t>1. Open 'Place Order'
 2. Enter valid Name/Card, invalid Month &amp; Year
 3. Click 'Purchase'</t>
   </si>
   <si>
-    <t xml:space="preserve">Purchase rejected with an expiry validation message</t>
+    <t>Purchase rejected with an expiry validation message</t>
   </si>
   <si>
     <t>OD-011</t>
   </si>
   <si>
-    <t xml:space="preserve">Place order with empty cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cart is empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open 'Cart'
+    <t>Place order with empty cart</t>
+  </si>
+  <si>
+    <t>Cart is empty</t>
+  </si>
+  <si>
+    <t>1. Open 'Cart'
 2. Click 'Place Order'
 3. Fill valid data, click 'Purchase'</t>
   </si>
   <si>
-    <t xml:space="preserve">Order is blocked (button disabled or message 'Cart is empty'); no confirmation with Amount 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likely defect if a 0 USD order is confirmed</t>
+    <t>Order is blocked (button disabled or message 'Cart is empty'); no confirmation with Amount 0</t>
+  </si>
+  <si>
+    <t>Likely defect if a 0 USD order is confirmed</t>
   </si>
   <si>
     <t>OD-012</t>
   </si>
   <si>
-    <t xml:space="preserve">Special / Unicode characters in Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name: Trần Nam &lt;b&gt;QA&lt;/b&gt;; Card: 4111111111111111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Place order with the given name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirmation shows the name as plain text (no HTML rendered)</t>
+    <t>Special / Unicode characters in Name</t>
+  </si>
+  <si>
+    <t>Name: Trần Nam &lt;b&gt;QA&lt;/b&gt;; Card: 4111111111111111</t>
+  </si>
+  <si>
+    <t>1. Place order with the given name</t>
+  </si>
+  <si>
+    <t>Confirmation shows the name as plain text (no HTML rendered)</t>
   </si>
   <si>
     <t>OD-013</t>
   </si>
   <si>
-    <t xml:space="preserve">Very long Name and Card (255 chars)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name: 'N' x 255; Card: '4' x 255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Place order with long values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Request handled gracefully: confirmation or validation message; no UI break, no server error</t>
+    <t>Very long Name and Card (255 chars)</t>
+  </si>
+  <si>
+    <t>Name: 'N' x 255; Card: '4' x 255</t>
+  </si>
+  <si>
+    <t>1. Place order with long values</t>
+  </si>
+  <si>
+    <t>Request handled gracefully: confirmation or validation message; no UI break, no server error</t>
   </si>
   <si>
     <t>OD-014</t>
   </si>
   <si>
-    <t xml:space="preserve">Cart unchanged after browser Back from purchase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete purchase and click 'OK'
+    <t>Cart unchanged after browser Back from purchase</t>
+  </si>
+  <si>
+    <t>1. Complete purchase and click 'OK'
 2. Press browser Back
 3. Open 'Cart'</t>
   </si>
   <si>
-    <t xml:space="preserve">Cart is empty; purchased item does not reappear</t>
+    <t>Cart is empty; purchased item does not reappear</t>
+  </si>
+  <si>
+    <t>Place Order' opens order form with total</t>
+  </si>
+  <si>
+    <t>Month is not correct. 
+Expected: Oct
+Actual: Sep</t>
+  </si>
+  <si>
+    <t>// Clicking OK before the popup's opening animation ends (no "visible" class yet) only closes it: the site never goes to index.html and the Place order modal keeps blocking the page</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.000000"/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="14.000000"/>
+      <sz val="14"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10.000000"/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10.000000"/>
+      <sz val="10"/>
       <color indexed="65"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="9.000000"/>
+      <sz val="9"/>
       <color rgb="FF8C8C8C"/>
       <name val="Courier New"/>
     </font>
@@ -1334,11 +1356,11 @@
   </fills>
   <borders count="2">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1353,364 +1375,1108 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+  <cellXfs count="21">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="4" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="129">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1762,7 +2528,7 @@
         <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1874,28 +2640,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr filterMode="0">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="1" width="26"/>
-    <col customWidth="1" min="2" max="6" style="1" width="14"/>
-    <col customWidth="1" min="7" max="7" width="14.421875"/>
+    <col min="1" max="1" width="26" style="1" customWidth="1"/>
+    <col min="2" max="6" width="14" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.350000000000001" customHeight="1">
+    <row r="1" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1903,7 +2667,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1911,7 +2675,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -1919,7 +2683,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -1927,7 +2691,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
@@ -1935,7 +2699,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
@@ -1955,7 +2719,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
+    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>17</v>
       </c>
@@ -1980,7 +2744,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
+    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>18</v>
       </c>
@@ -2005,7 +2769,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
+    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>19</v>
       </c>
@@ -2030,7 +2794,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>15</v>
       </c>
@@ -2055,12 +2819,12 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>11</v>
       </c>
@@ -2083,7 +2847,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
@@ -2112,7 +2876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
@@ -2141,17 +2905,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="7">
         <f>COUNTIF(Order!$M:$M,"Pass")</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C20" s="7">
         <f>COUNTIF(Order!$M:$M,"Fail")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D20" s="7">
         <f>COUNTIF(Order!$M:$M,"Blocked")</f>
@@ -2159,19 +2923,19 @@
       </c>
       <c r="E20" s="7">
         <f>COUNTIF(Order!$M:$M,"Not Run")</f>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F20" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="G20" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1"/>
-    <row r="22" ht="15" customHeight="1">
+        <v>0.7857142857142857</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="13"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
@@ -2180,7 +2944,7 @@
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
     </row>
-    <row r="23" ht="15" customHeight="1">
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2189,7 +2953,7 @@
       <c r="F23" s="13"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" ht="15" customHeight="1">
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -2198,7 +2962,7 @@
       <c r="F24" s="13"/>
       <c r="G24" s="13"/>
     </row>
-    <row r="25" ht="15" customHeight="1">
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -2207,7 +2971,7 @@
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" ht="15" customHeight="1">
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
@@ -2216,7 +2980,7 @@
       <c r="F26" s="13"/>
       <c r="G26" s="13"/>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="13"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -2225,7 +2989,7 @@
       <c r="F27" s="13"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" ht="15" customHeight="1">
+    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="13"/>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -2234,7 +2998,7 @@
       <c r="F28" s="13"/>
       <c r="G28" s="13"/>
     </row>
-    <row r="29" ht="14.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="13"/>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -2244,37 +3008,32 @@
       <c r="G29" s="13"/>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr filterMode="0">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:O26"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="1" width="10"/>
-    <col customWidth="1" min="2" max="2" style="1" width="9"/>
-    <col customWidth="1" min="3" max="3" style="1" width="16"/>
-    <col customWidth="1" min="4" max="4" style="1" width="38"/>
-    <col customWidth="1" min="5" max="5" style="1" width="11"/>
-    <col customWidth="1" min="6" max="6" style="1" width="9"/>
-    <col customWidth="1" min="7" max="8" style="1" width="30"/>
-    <col customWidth="1" min="9" max="10" style="1" width="52"/>
-    <col customWidth="1" min="11" max="11" style="1" width="11"/>
-    <col customWidth="1" min="12" max="12" style="1" width="34"/>
-    <col customWidth="1" min="13" max="13" style="1" width="11"/>
-    <col customWidth="1" min="14" max="14" style="1" width="28"/>
-    <col customWidth="1" min="15" max="15" style="1" width="34"/>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="38" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1" customWidth="1"/>
+    <col min="7" max="8" width="30" style="1" customWidth="1"/>
+    <col min="9" max="10" width="52" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11" style="1" customWidth="1"/>
+    <col min="12" max="12" width="34" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11" style="1" customWidth="1"/>
+    <col min="14" max="14" width="28" style="1" customWidth="1"/>
+    <col min="15" max="15" width="34" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.850000000000001" customHeight="1">
+    <row r="1" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
         <v>27</v>
       </c>
@@ -2321,7 +3080,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" ht="35.049999999999997" customHeight="1">
+    <row r="2" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>41</v>
       </c>
@@ -2364,7 +3123,7 @@
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
     </row>
-    <row r="3" ht="46.25" customHeight="1">
+    <row r="3" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>51</v>
       </c>
@@ -2407,7 +3166,7 @@
       <c r="N3" s="15"/>
       <c r="O3" s="15"/>
     </row>
-    <row r="4" ht="23.850000000000001" customHeight="1">
+    <row r="4" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>60</v>
       </c>
@@ -2450,7 +3209,7 @@
       <c r="N4" s="15"/>
       <c r="O4" s="15"/>
     </row>
-    <row r="5" ht="46.25" customHeight="1">
+    <row r="5" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>67</v>
       </c>
@@ -2493,7 +3252,7 @@
       <c r="N5" s="15"/>
       <c r="O5" s="15"/>
     </row>
-    <row r="6" ht="35.049999999999997" customHeight="1">
+    <row r="6" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>72</v>
       </c>
@@ -2536,7 +3295,7 @@
       <c r="N6" s="15"/>
       <c r="O6" s="15"/>
     </row>
-    <row r="7" ht="35.049999999999997" customHeight="1">
+    <row r="7" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>78</v>
       </c>
@@ -2579,7 +3338,7 @@
       <c r="N7" s="15"/>
       <c r="O7" s="15"/>
     </row>
-    <row r="8" ht="35.049999999999997" customHeight="1">
+    <row r="8" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>83</v>
       </c>
@@ -2622,7 +3381,7 @@
       <c r="N8" s="15"/>
       <c r="O8" s="15"/>
     </row>
-    <row r="9" ht="35.049999999999997" customHeight="1">
+    <row r="9" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
         <v>88</v>
       </c>
@@ -2667,7 +3426,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="10" ht="46.25" customHeight="1">
+    <row r="10" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
         <v>95</v>
       </c>
@@ -2712,7 +3471,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" ht="35.049999999999997" customHeight="1">
+    <row r="11" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
         <v>102</v>
       </c>
@@ -2755,7 +3514,7 @@
       <c r="N11" s="15"/>
       <c r="O11" s="15"/>
     </row>
-    <row r="12" ht="35.049999999999997" customHeight="1">
+    <row r="12" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
         <v>109</v>
       </c>
@@ -2798,7 +3557,7 @@
       <c r="N12" s="15"/>
       <c r="O12" s="15"/>
     </row>
-    <row r="13" ht="35.049999999999997" customHeight="1">
+    <row r="13" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
         <v>113</v>
       </c>
@@ -2841,7 +3600,7 @@
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
     </row>
-    <row r="14" ht="46.25" customHeight="1">
+    <row r="14" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
         <v>117</v>
       </c>
@@ -2884,7 +3643,7 @@
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
     </row>
-    <row r="15" ht="35.049999999999997" customHeight="1">
+    <row r="15" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
         <v>124</v>
       </c>
@@ -2927,7 +3686,7 @@
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
     </row>
-    <row r="16" ht="46.25" customHeight="1">
+    <row r="16" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
         <v>129</v>
       </c>
@@ -2970,7 +3729,7 @@
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
     </row>
-    <row r="17" ht="35.049999999999997" customHeight="1">
+    <row r="17" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
         <v>133</v>
       </c>
@@ -3015,7 +3774,7 @@
       </c>
       <c r="O17" s="15"/>
     </row>
-    <row r="18" ht="35.049999999999997" customHeight="1">
+    <row r="18" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
         <v>139</v>
       </c>
@@ -3058,7 +3817,7 @@
       <c r="N18" s="15"/>
       <c r="O18" s="15"/>
     </row>
-    <row r="19" ht="35.049999999999997" customHeight="1">
+    <row r="19" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
         <v>145</v>
       </c>
@@ -3101,7 +3860,7 @@
       <c r="N19" s="15"/>
       <c r="O19" s="15"/>
     </row>
-    <row r="20" ht="46.25" customHeight="1">
+    <row r="20" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
         <v>150</v>
       </c>
@@ -3146,7 +3905,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="21" ht="46.25" customHeight="1">
+    <row r="21" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="15" t="s">
         <v>156</v>
       </c>
@@ -3191,7 +3950,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="22" ht="35.049999999999997" customHeight="1">
+    <row r="22" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="15" t="s">
         <v>162</v>
       </c>
@@ -3236,7 +3995,7 @@
       </c>
       <c r="O22" s="15"/>
     </row>
-    <row r="23" ht="46.25" customHeight="1">
+    <row r="23" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="15" t="s">
         <v>168</v>
       </c>
@@ -3279,7 +4038,7 @@
       <c r="N23" s="15"/>
       <c r="O23" s="15"/>
     </row>
-    <row r="24" ht="23.850000000000001" customHeight="1">
+    <row r="24" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="15" t="s">
         <v>172</v>
       </c>
@@ -3322,7 +4081,7 @@
       <c r="N24" s="15"/>
       <c r="O24" s="15"/>
     </row>
-    <row r="25" ht="46.25" customHeight="1">
+    <row r="25" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="15" t="s">
         <v>177</v>
       </c>
@@ -3365,7 +4124,7 @@
       <c r="N25" s="15"/>
       <c r="O25" s="15"/>
     </row>
-    <row r="26" ht="23.850000000000001" customHeight="1">
+    <row r="26" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="15" t="s">
         <v>181</v>
       </c>
@@ -3409,1725 +4168,609 @@
       <c r="O26" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O26"/>
-  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <autoFilter ref="A1:O26" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <conditionalFormatting sqref="M2:M26">
+    <cfRule type="cellIs" dxfId="128" priority="2" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M26">
+    <cfRule type="cellIs" dxfId="127" priority="3" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M26">
+    <cfRule type="cellIs" dxfId="126" priority="4" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M18">
+    <cfRule type="cellIs" dxfId="125" priority="5" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M18">
+    <cfRule type="cellIs" dxfId="124" priority="6" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M18">
+    <cfRule type="cellIs" dxfId="123" priority="7" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M19">
+    <cfRule type="cellIs" dxfId="122" priority="8" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M19">
+    <cfRule type="cellIs" dxfId="121" priority="9" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M19">
+    <cfRule type="cellIs" dxfId="120" priority="10" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M19">
+    <cfRule type="cellIs" dxfId="119" priority="11" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M19">
+    <cfRule type="cellIs" dxfId="118" priority="12" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M19">
+    <cfRule type="cellIs" dxfId="117" priority="13" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M20">
+    <cfRule type="cellIs" dxfId="116" priority="14" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M20">
+    <cfRule type="cellIs" dxfId="115" priority="15" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M20">
+    <cfRule type="cellIs" dxfId="114" priority="16" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M20">
+    <cfRule type="cellIs" dxfId="113" priority="17" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M20">
+    <cfRule type="cellIs" dxfId="112" priority="18" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M20">
+    <cfRule type="cellIs" dxfId="111" priority="19" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M20">
+    <cfRule type="cellIs" dxfId="110" priority="20" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M20">
+    <cfRule type="cellIs" dxfId="109" priority="21" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M20">
+    <cfRule type="cellIs" dxfId="108" priority="22" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M21">
+    <cfRule type="cellIs" dxfId="107" priority="23" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M21">
+    <cfRule type="cellIs" dxfId="106" priority="24" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M21">
+    <cfRule type="cellIs" dxfId="105" priority="25" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M21">
+    <cfRule type="cellIs" dxfId="104" priority="26" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M21">
+    <cfRule type="cellIs" dxfId="103" priority="27" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M21">
+    <cfRule type="cellIs" dxfId="102" priority="28" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M21">
+    <cfRule type="cellIs" dxfId="101" priority="29" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M21">
+    <cfRule type="cellIs" dxfId="100" priority="30" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M21">
+    <cfRule type="cellIs" dxfId="99" priority="31" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M21">
+    <cfRule type="cellIs" dxfId="98" priority="32" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M21">
+    <cfRule type="cellIs" dxfId="97" priority="33" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M21">
+    <cfRule type="cellIs" dxfId="96" priority="34" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M22">
+    <cfRule type="cellIs" dxfId="95" priority="35" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M22">
+    <cfRule type="cellIs" dxfId="94" priority="36" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M22">
+    <cfRule type="cellIs" dxfId="93" priority="37" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23">
+    <cfRule type="cellIs" dxfId="92" priority="38" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23">
+    <cfRule type="cellIs" dxfId="91" priority="39" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23">
+    <cfRule type="cellIs" dxfId="90" priority="40" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23">
+    <cfRule type="cellIs" dxfId="89" priority="41" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23">
+    <cfRule type="cellIs" dxfId="88" priority="42" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23">
+    <cfRule type="cellIs" dxfId="87" priority="43" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23">
+    <cfRule type="cellIs" dxfId="86" priority="44" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23">
+    <cfRule type="cellIs" dxfId="85" priority="45" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23">
+    <cfRule type="cellIs" dxfId="84" priority="46" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23">
+    <cfRule type="cellIs" dxfId="83" priority="47" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23">
+    <cfRule type="cellIs" dxfId="82" priority="48" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23">
+    <cfRule type="cellIs" dxfId="81" priority="49" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23">
+    <cfRule type="cellIs" dxfId="80" priority="50" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23">
+    <cfRule type="cellIs" dxfId="79" priority="51" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23">
+    <cfRule type="cellIs" dxfId="78" priority="52" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="77" priority="53" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="76" priority="54" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="75" priority="55" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="74" priority="56" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="73" priority="57" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="72" priority="58" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="71" priority="59" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="70" priority="60" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="69" priority="61" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="68" priority="62" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="67" priority="63" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="66" priority="64" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="65" priority="65" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="64" priority="66" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="63" priority="67" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="62" priority="68" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="61" priority="69" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="cellIs" dxfId="60" priority="70" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="59" priority="71" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="58" priority="72" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="57" priority="73" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="56" priority="74" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="55" priority="75" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="54" priority="76" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="53" priority="77" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="52" priority="78" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="51" priority="79" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="50" priority="80" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="49" priority="81" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="48" priority="82" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="47" priority="83" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="46" priority="84" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="45" priority="85" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="44" priority="86" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="43" priority="87" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="42" priority="88" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="41" priority="89" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="40" priority="90" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="cellIs" dxfId="39" priority="91" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="38" priority="92" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="37" priority="93" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="36" priority="94" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="35" priority="95" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="34" priority="96" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="33" priority="97" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="32" priority="98" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="31" priority="99" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="30" priority="100" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="29" priority="101" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="28" priority="102" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="27" priority="103" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="26" priority="104" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="25" priority="105" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="24" priority="106" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="23" priority="107" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="22" priority="108" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="21" priority="109" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="20" priority="110" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="19" priority="111" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="18" priority="112" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="17" priority="113" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="16" priority="114" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26">
+    <cfRule type="cellIs" dxfId="15" priority="115" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="M2:M16 M23:M26 M18:M21" xr:uid="{7D526BDB-C970-4102-88CF-19C2D028DEC3}">
+      <formula1>"Not Run,Pass,Fail,Blocked,Skipped"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M2:M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M2:M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M2:M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="5" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M18</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="6" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M18</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="7" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M18</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="8" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="9" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="10" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="11" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="12" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="13" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="14" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M20</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="15" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M20</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="16" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M20</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="17" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M20</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="18" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M20</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="19" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M20</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="20" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M20</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="21" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M20</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="22" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M20</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="23" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M21</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="24" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M21</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="25" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M21</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="26" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M21</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="27" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M21</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="28" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M21</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="29" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M21</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="30" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M21</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="31" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M21</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="32" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M21</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="33" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M21</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="34" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M21</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="35" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M22</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="36" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M22</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="37" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M22</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="38" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="39" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="40" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="41" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="42" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="43" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="44" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="45" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="46" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="47" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="48" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="49" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="50" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="51" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="52" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="53" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="54" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="55" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="56" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="57" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="58" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="59" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="60" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="61" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="62" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="63" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="64" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="65" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="66" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="67" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="68" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="69" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="70" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="71" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="72" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="73" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="74" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="75" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="76" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="77" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="78" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="79" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="80" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="81" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="82" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="83" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="84" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="85" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="86" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="87" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="88" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="89" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="90" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="91" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="92" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="93" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="94" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="95" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="96" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="97" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="98" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="99" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="100" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="101" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="102" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="103" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="104" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="105" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="106" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="107" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="108" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="109" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="110" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="111" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="112" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="113" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="114" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="115" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M26</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9" disablePrompts="0">
-        <x14:dataValidation xr:uid="{7D526BDB-C970-4102-88CF-19C2D028DEC3}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>M2:M16</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{153BD1CA-CFD0-4112-B0C0-0B1B9E57E002}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>M18</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{10040218-07D9-4C18-A47C-51986CB9FD68}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>M19</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{391196E1-7DD8-42D8-B7E3-A7F2A5781A84}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>M20</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{24D52F3B-93E5-4154-A04D-A55F6843B748}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>M21</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{412ADD45-4CCF-4022-B95D-4C73F5B82CF2}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>M23</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{65667420-CC0D-4FCA-B6F9-F172EB96EA05}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>M24</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{3D30BD1A-BF25-4BEA-8E6F-728FCEDAD285}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>M25</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{58F08322-8017-4C55-B344-74A1B86959E4}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>M26</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr filterMode="0">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:O33"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="1" width="10"/>
-    <col customWidth="1" min="2" max="2" style="1" width="9"/>
-    <col customWidth="1" min="3" max="3" style="1" width="16"/>
-    <col customWidth="1" min="4" max="4" style="1" width="38"/>
-    <col customWidth="1" min="5" max="5" style="1" width="11"/>
-    <col customWidth="1" min="6" max="6" style="1" width="9"/>
-    <col customWidth="1" min="7" max="8" style="1" width="30"/>
-    <col customWidth="1" min="9" max="10" style="1" width="52"/>
-    <col customWidth="1" min="11" max="11" style="1" width="11"/>
-    <col customWidth="1" min="12" max="12" style="1" width="34"/>
-    <col customWidth="1" min="13" max="13" style="1" width="11"/>
-    <col customWidth="1" min="14" max="14" style="1" width="28"/>
-    <col customWidth="1" min="15" max="15" style="1" width="34"/>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="38" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1" customWidth="1"/>
+    <col min="7" max="8" width="30" style="1" customWidth="1"/>
+    <col min="9" max="10" width="52" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11" style="1" customWidth="1"/>
+    <col min="12" max="12" width="34" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11" style="1" customWidth="1"/>
+    <col min="14" max="14" width="28" style="1" customWidth="1"/>
+    <col min="15" max="15" width="34" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.850000000000001" customHeight="1">
+    <row r="1" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
         <v>27</v>
       </c>
@@ -5174,7 +4817,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" ht="46.25" customHeight="1">
+    <row r="2" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>189</v>
       </c>
@@ -5217,7 +4860,7 @@
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
     </row>
-    <row r="3" ht="46.25" customHeight="1">
+    <row r="3" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>196</v>
       </c>
@@ -5260,7 +4903,7 @@
       <c r="N3" s="15"/>
       <c r="O3" s="15"/>
     </row>
-    <row r="4" ht="35.049999999999997" customHeight="1">
+    <row r="4" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>202</v>
       </c>
@@ -5303,7 +4946,7 @@
       <c r="N4" s="15"/>
       <c r="O4" s="15"/>
     </row>
-    <row r="5" ht="35.049999999999997" customHeight="1">
+    <row r="5" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>207</v>
       </c>
@@ -5348,7 +4991,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="6" ht="23.850000000000001" customHeight="1">
+    <row r="6" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>213</v>
       </c>
@@ -5391,7 +5034,7 @@
       <c r="N6" s="15"/>
       <c r="O6" s="15"/>
     </row>
-    <row r="7" ht="23.850000000000001" customHeight="1">
+    <row r="7" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>220</v>
       </c>
@@ -5434,7 +5077,7 @@
       <c r="N7" s="15"/>
       <c r="O7" s="15"/>
     </row>
-    <row r="8" ht="23.850000000000001" customHeight="1">
+    <row r="8" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>224</v>
       </c>
@@ -5477,7 +5120,7 @@
       <c r="N8" s="15"/>
       <c r="O8" s="15"/>
     </row>
-    <row r="9" ht="57.450000000000003" customHeight="1">
+    <row r="9" spans="1:15" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
         <v>231</v>
       </c>
@@ -5520,7 +5163,7 @@
       <c r="N9" s="15"/>
       <c r="O9" s="15"/>
     </row>
-    <row r="10" ht="35.049999999999997" customHeight="1">
+    <row r="10" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
         <v>236</v>
       </c>
@@ -5563,7 +5206,7 @@
       <c r="N10" s="15"/>
       <c r="O10" s="15"/>
     </row>
-    <row r="11" ht="35.049999999999997" customHeight="1">
+    <row r="11" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
         <v>243</v>
       </c>
@@ -5606,7 +5249,7 @@
       <c r="N11" s="15"/>
       <c r="O11" s="15"/>
     </row>
-    <row r="12" ht="35.049999999999997" customHeight="1">
+    <row r="12" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
         <v>248</v>
       </c>
@@ -5649,7 +5292,7 @@
       <c r="N12" s="15"/>
       <c r="O12" s="15"/>
     </row>
-    <row r="13" ht="23.850000000000001" customHeight="1">
+    <row r="13" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
         <v>253</v>
       </c>
@@ -5692,7 +5335,7 @@
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
     </row>
-    <row r="14" ht="23.850000000000001" customHeight="1">
+    <row r="14" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
         <v>260</v>
       </c>
@@ -5735,7 +5378,7 @@
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
     </row>
-    <row r="15" ht="23.850000000000001" customHeight="1">
+    <row r="15" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
         <v>267</v>
       </c>
@@ -5778,7 +5421,7 @@
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
     </row>
-    <row r="16" ht="35.049999999999997" customHeight="1">
+    <row r="16" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
         <v>272</v>
       </c>
@@ -5823,7 +5466,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="17" ht="23.850000000000001" customHeight="1">
+    <row r="17" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
         <v>278</v>
       </c>
@@ -5866,7 +5509,7 @@
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
     </row>
-    <row r="18" ht="35.049999999999997" customHeight="1">
+    <row r="18" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
         <v>283</v>
       </c>
@@ -5909,7 +5552,7 @@
       <c r="N18" s="15"/>
       <c r="O18" s="15"/>
     </row>
-    <row r="19" ht="46.25" customHeight="1">
+    <row r="19" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
         <v>287</v>
       </c>
@@ -5952,249 +5595,113 @@
       <c r="N19" s="15"/>
       <c r="O19" s="15"/>
     </row>
-    <row r="20" ht="46.25" customHeight="1"/>
-    <row r="21" ht="35.049999999999997" customHeight="1"/>
-    <row r="22" ht="35.049999999999997" customHeight="1"/>
-    <row r="23" ht="35.049999999999997" customHeight="1"/>
-    <row r="24" ht="23.850000000000001" customHeight="1"/>
-    <row r="25" ht="23.850000000000001" customHeight="1"/>
-    <row r="26" ht="23.850000000000001" customHeight="1"/>
-    <row r="27" ht="35.049999999999997" customHeight="1"/>
-    <row r="28" ht="23.850000000000001" customHeight="1"/>
-    <row r="29" ht="35.049999999999997" customHeight="1"/>
-    <row r="30" ht="23.850000000000001" customHeight="1"/>
-    <row r="31" ht="23.850000000000001" customHeight="1"/>
-    <row r="32" ht="35.049999999999997" customHeight="1"/>
-    <row r="33" ht="46.25" customHeight="1"/>
+    <row r="20" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="24" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="33" ht="46.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <autoFilter ref="A1:O19"/>
-  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <autoFilter ref="A1:O19" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <conditionalFormatting sqref="M2:M19">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M19">
+    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M19">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M15:M16">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M15:M16">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M15:M16">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M17:M19">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M17:M19">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M17:M19">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M17:M19">
+    <cfRule type="cellIs" dxfId="5" priority="11" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M17:M19">
+    <cfRule type="cellIs" dxfId="4" priority="12" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M17:M19">
+    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="M2:M19" xr:uid="{523F2BC9-A78A-4AF6-95EB-35D661DC0BF7}">
+      <formula1>"Not Run,Pass,Fail,Blocked,Skipped"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M2:M19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M2:M19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M2:M19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M15:M16</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M15:M16</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M15:M16</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M17:M19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M17:M19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M17:M19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M17:M19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M17:M19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M17:M19</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3" disablePrompts="0">
-        <x14:dataValidation xr:uid="{523F2BC9-A78A-4AF6-95EB-35D661DC0BF7}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
-          </x14:formula1>
-          <xm:sqref>M2:M14</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{41A20C3C-8B84-4CF1-9E96-9528D1DC79EF}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
-          </x14:formula1>
-          <xm:sqref>M15:M16</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{668078D8-A191-41E2-B1B4-75B364D4C617}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
-          </x14:formula1>
-          <xm:sqref>M17:M19</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr filterMode="0">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:O33"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="1" width="10"/>
-    <col customWidth="1" min="2" max="2" style="1" width="9"/>
-    <col customWidth="1" min="3" max="3" style="1" width="16"/>
-    <col customWidth="1" min="4" max="4" style="1" width="38"/>
-    <col customWidth="1" min="5" max="5" style="1" width="11"/>
-    <col customWidth="1" min="6" max="6" style="1" width="9"/>
-    <col customWidth="1" min="7" max="8" style="1" width="30"/>
-    <col customWidth="1" min="9" max="10" style="1" width="52"/>
-    <col customWidth="1" min="11" max="11" style="1" width="11"/>
-    <col customWidth="1" min="12" max="12" style="1" width="34"/>
-    <col customWidth="1" min="13" max="13" style="1" width="11"/>
-    <col customWidth="1" min="14" max="14" style="1" width="28"/>
-    <col customWidth="1" min="15" max="15" style="1" width="34"/>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="38" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1" customWidth="1"/>
+    <col min="7" max="8" width="30" style="1" customWidth="1"/>
+    <col min="9" max="10" width="52" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11" style="1" customWidth="1"/>
+    <col min="12" max="12" width="34" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11" style="1" customWidth="1"/>
+    <col min="14" max="14" width="28" style="1" customWidth="1"/>
+    <col min="15" max="15" width="34" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.850000000000001" customHeight="1">
+    <row r="1" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
         <v>27</v>
       </c>
@@ -6241,7 +5748,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" ht="23.850000000000001" customHeight="1">
+    <row r="2" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>293</v>
       </c>
@@ -6251,8 +5758,8 @@
       <c r="C2" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="D2" s="15" t="s">
-        <v>295</v>
+      <c r="D2" s="20" t="s">
+        <v>363</v>
       </c>
       <c r="E2" s="16" t="s">
         <v>12</v>
@@ -6267,26 +5774,26 @@
         <v>46</v>
       </c>
       <c r="I2" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="J2" s="15" t="s">
         <v>296</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>297</v>
       </c>
       <c r="K2" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
     </row>
-    <row r="3" ht="68.650000000000006" customHeight="1">
+    <row r="3" spans="1:15" ht="68.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>19</v>
@@ -6295,7 +5802,7 @@
         <v>294</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E3" s="16" t="s">
         <v>12</v>
@@ -6307,29 +5814,29 @@
         <v>239</v>
       </c>
       <c r="H3" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="I3" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="J3" s="15" t="s">
         <v>302</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>303</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N3" s="15"/>
       <c r="O3" s="15"/>
     </row>
-    <row r="4" ht="35.049999999999997" customHeight="1">
+    <row r="4" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>19</v>
@@ -6338,7 +5845,7 @@
         <v>294</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>12</v>
@@ -6350,29 +5857,31 @@
         <v>216</v>
       </c>
       <c r="H4" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="I4" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="J4" s="15" t="s">
         <v>307</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>308</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" s="15"/>
+        <v>22</v>
+      </c>
+      <c r="N4" s="15" t="s">
+        <v>364</v>
+      </c>
       <c r="O4" s="15"/>
     </row>
-    <row r="5" ht="35.049999999999997" customHeight="1">
+    <row r="5" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>19</v>
@@ -6381,7 +5890,7 @@
         <v>294</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>12</v>
@@ -6393,29 +5902,31 @@
         <v>239</v>
       </c>
       <c r="H5" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="J5" s="15" t="s">
         <v>312</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>313</v>
       </c>
       <c r="K5" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M5" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-    </row>
-    <row r="6" ht="23.850000000000001" customHeight="1">
+      <c r="O5" s="15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>19</v>
@@ -6424,7 +5935,7 @@
         <v>294</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>13</v>
@@ -6436,29 +5947,29 @@
         <v>239</v>
       </c>
       <c r="H6" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="I6" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="J6" s="15" t="s">
         <v>317</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>318</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N6" s="15"/>
       <c r="O6" s="15"/>
     </row>
-    <row r="7" ht="35.049999999999997" customHeight="1">
+    <row r="7" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>19</v>
@@ -6467,7 +5978,7 @@
         <v>294</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>13</v>
@@ -6479,29 +5990,29 @@
         <v>239</v>
       </c>
       <c r="H7" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="I7" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="J7" s="15" t="s">
         <v>323</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>324</v>
       </c>
       <c r="K7" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N7" s="15"/>
       <c r="O7" s="15"/>
     </row>
-    <row r="8" ht="35.049999999999997" customHeight="1">
+    <row r="8" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>19</v>
@@ -6510,7 +6021,7 @@
         <v>294</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>13</v>
@@ -6522,29 +6033,29 @@
         <v>239</v>
       </c>
       <c r="H8" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="I8" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="I8" s="15" t="s">
-        <v>328</v>
-      </c>
       <c r="J8" s="15" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="K8" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N8" s="15"/>
       <c r="O8" s="15"/>
     </row>
-    <row r="9" ht="46.25" customHeight="1">
+    <row r="9" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>19</v>
@@ -6553,7 +6064,7 @@
         <v>294</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>13</v>
@@ -6565,29 +6076,29 @@
         <v>239</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I9" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="J9" s="15" t="s">
         <v>331</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>332</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N9" s="15"/>
       <c r="O9" s="15"/>
     </row>
-    <row r="10" ht="35.049999999999997" customHeight="1">
+    <row r="10" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>19</v>
@@ -6596,7 +6107,7 @@
         <v>294</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E10" s="18" t="s">
         <v>13</v>
@@ -6608,31 +6119,31 @@
         <v>239</v>
       </c>
       <c r="H10" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="I10" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="J10" s="15" t="s">
         <v>336</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>337</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N10" s="15"/>
       <c r="O10" s="15" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="15" t="s">
         <v>338</v>
-      </c>
-    </row>
-    <row r="11" ht="35.049999999999997" customHeight="1">
-      <c r="A11" s="15" t="s">
-        <v>339</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>19</v>
@@ -6641,7 +6152,7 @@
         <v>294</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E11" s="18" t="s">
         <v>13</v>
@@ -6653,31 +6164,31 @@
         <v>239</v>
       </c>
       <c r="H11" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="I11" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="J11" s="15" t="s">
         <v>342</v>
-      </c>
-      <c r="J11" s="15" t="s">
-        <v>343</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N11" s="15"/>
       <c r="O11" s="15" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="12" ht="35.049999999999997" customHeight="1">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>19</v>
@@ -6686,7 +6197,7 @@
         <v>294</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E12" s="18" t="s">
         <v>13</v>
@@ -6695,34 +6206,34 @@
         <v>44</v>
       </c>
       <c r="G12" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="I12" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="H12" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="I12" s="15" t="s">
+      <c r="J12" s="15" t="s">
         <v>347</v>
-      </c>
-      <c r="J12" s="15" t="s">
-        <v>348</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M12" s="15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N12" s="15"/>
       <c r="O12" s="15" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="15" t="s">
         <v>349</v>
-      </c>
-    </row>
-    <row r="13" ht="23.850000000000001" customHeight="1">
-      <c r="A13" s="15" t="s">
-        <v>350</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>19</v>
@@ -6731,7 +6242,7 @@
         <v>294</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>14</v>
@@ -6743,19 +6254,19 @@
         <v>239</v>
       </c>
       <c r="H13" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="I13" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="J13" s="15" t="s">
         <v>353</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>354</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M13" s="15" t="s">
         <v>24</v>
@@ -6763,9 +6274,9 @@
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
     </row>
-    <row r="14" ht="23.850000000000001" customHeight="1">
+    <row r="14" spans="1:15" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>19</v>
@@ -6774,7 +6285,7 @@
         <v>294</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>14</v>
@@ -6786,19 +6297,19 @@
         <v>239</v>
       </c>
       <c r="H14" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="I14" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="J14" s="15" t="s">
         <v>358</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>359</v>
       </c>
       <c r="K14" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M14" s="15" t="s">
         <v>24</v>
@@ -6806,9 +6317,9 @@
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
     </row>
-    <row r="15" ht="35.049999999999997" customHeight="1">
+    <row r="15" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>19</v>
@@ -6817,7 +6328,7 @@
         <v>225</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>14</v>
@@ -6829,19 +6340,19 @@
         <v>239</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I15" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="J15" s="15" t="s">
         <v>362</v>
-      </c>
-      <c r="J15" s="15" t="s">
-        <v>363</v>
       </c>
       <c r="K15" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M15" s="15" t="s">
         <v>24</v>
@@ -6849,87 +6360,47 @@
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
     </row>
-    <row r="16" ht="35.049999999999997" customHeight="1"/>
-    <row r="17" ht="23.850000000000001" customHeight="1"/>
-    <row r="18" ht="35.049999999999997" customHeight="1"/>
-    <row r="19" ht="35.049999999999997" customHeight="1"/>
-    <row r="20" ht="46.25" customHeight="1"/>
-    <row r="21" ht="35.049999999999997" customHeight="1"/>
-    <row r="22" ht="35.049999999999997" customHeight="1"/>
-    <row r="23" ht="35.049999999999997" customHeight="1"/>
-    <row r="24" ht="23.850000000000001" customHeight="1"/>
-    <row r="25" ht="23.850000000000001" customHeight="1"/>
-    <row r="26" ht="23.850000000000001" customHeight="1"/>
-    <row r="27" ht="35.049999999999997" customHeight="1"/>
-    <row r="28" ht="23.850000000000001" customHeight="1"/>
-    <row r="29" ht="35.049999999999997" customHeight="1"/>
-    <row r="30" ht="23.850000000000001" customHeight="1"/>
-    <row r="31" ht="23.850000000000001" customHeight="1"/>
-    <row r="32" ht="35.049999999999997" customHeight="1"/>
-    <row r="33" ht="46.25" customHeight="1"/>
+    <row r="16" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="17" ht="23.9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="18" ht="35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="19" ht="35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="20" ht="46.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="21" ht="35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="22" ht="35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" ht="35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="24" ht="23.9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="25" ht="23.9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" ht="23.9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="27" ht="35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="28" ht="23.9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="29" ht="35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" ht="23.9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="31" ht="23.9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="32" ht="35" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="33" ht="46.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <autoFilter ref="A1:O15"/>
-  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <autoFilter ref="A1:O15" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <conditionalFormatting sqref="M2:M15">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M15">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M15">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="M2:M15" xr:uid="{1BA9D181-C2EF-4231-9122-93ACF90C89AB}">
+      <formula1>"Not Run,Pass,Fail,Blocked,Skipped"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Pass"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M2:M15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Fail"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M2:M15</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="">
-            <xm:f>"Blocked"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFEB9C"/>
-                  <bgColor rgb="FFFFEB9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>M2:M15</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{1BA9D181-C2EF-4231-9122-93ACF90C89AB}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>"Not Run,Pass,Fail,Blocked,Skipped"</xm:f>
-          </x14:formula1>
-          <xm:sqref>M2:M15</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>